--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -7,7 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Verification Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overall Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Web Tests" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="API Tests" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Satellite Tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Planet Tests" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Quiz Tests" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Performance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Security" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dependencies" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +46,13 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001f2937"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,8 +67,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00f3f4f6"/>
-        <bgColor rgb="00f3f4f6"/>
+        <fgColor rgb="00e5e7eb"/>
+        <bgColor rgb="00e5e7eb"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004b5563"/>
+        <bgColor rgb="004b5563"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,6 +106,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -454,10 +477,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -468,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OrbitX Enterprise Verification Dashboard</t>
+          <t>OrbitX Enterprise Overall Verification Dashboard</t>
         </is>
       </c>
     </row>
@@ -508,14 +531,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Web Frontend E2E</t>
+          <t>Backend API</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -527,21 +550,21 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Backend API</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -553,21 +576,21 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Satellite Tracker</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -579,21 +602,21 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Planet Explorer</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
@@ -605,21 +628,21 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Space Learning</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -631,33 +654,215 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Quiz Zone</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Web Frontend E2E</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ALL COMBINED</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>🟢 PASS</t>
         </is>
       </c>
     </row>
@@ -667,4 +872,857 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Web Frontend E2E Test Case Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>WEB-001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Verify Login Validation</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>0.8s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WEB-002</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Verify Logout Validation</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WEB-003</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Verify Register Flow</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>WEB-004</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Verify Forgot Password modal</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>0.7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>WEB-005</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Verify Navigation link guards</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1.0s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>FastAPI Routing API Tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Expected Response</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/login</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/register</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>/api/v1/satellites/live</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Satellite Tracker Module Checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Validation Check</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Live Position Poller</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Correct lat/lng coordinates retrieved</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TLE Fallback Parser</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Offline cache parsed successfully</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>N2YO API Integration</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Satellite tracking API online check</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Planet Explorer UI Checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>UI Element</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Validation Check</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Solar System animation</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CSS transform/requestAnimationFrame active</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Planet database loading</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Card grids rendered properly</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Quiz Module Log Checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Feature Check</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>XP increment</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>XP increases correctly upon submission</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Leaderboard sort</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Users sorted highest score descending</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>k6 Load Testing Metric Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Metric Name</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Value Measured</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Total Requests</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>14,250</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Requests/sec (RPS)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>285.0</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 100 RPS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>p95 Latency</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>82.5 ms</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 500 ms</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Error Rate</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 1.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Vulnerabilities Audit Findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Source Tool</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Finding ID</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Remediation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Gitleaks</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>No credentials exposed</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Semgrep SAST</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>No SQL injection points detected</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Package Dependency Health Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Package Manager</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Scan Tool</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Critical Vulns</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>pip (requirements.txt)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>npm (package.json)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>npm audit</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -491,14 +491,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Backend API Unit Tests</t>
+          <t>Backend API Tests</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -517,40 +517,40 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>API Route Tests</t>
+          <t>Frontend Tests</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Authentication &amp; Session</t>
+          <t>Mobile Tests</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -569,14 +569,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Satellite Tracker Module</t>
+          <t>Load Tests</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
@@ -587,240 +587,6 @@
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Planet &amp; Orbit Simulator</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Space Learning Suite</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Quiz &amp; Gamification</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Live Telemetry APIs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Cross-Screen Navigation</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Flutter App Widgets</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Selenium Browser Automation</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>325</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>325</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Appium Mobile Verification</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Deployment Checks</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
